--- a/0_일정관리/일정.xlsx
+++ b/0_일정관리/일정.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{23728F7F-3F9C-4CBE-BA74-F3C304C93E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{6E401FD5-689D-4F8A-AD59-0AA7F197EAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21660" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -713,7 +713,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <row r="2" spans="1:28" ht="21" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="37" t="s">
         <v>2</v>
@@ -1108,8 +1108,8 @@
       <c r="N12" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
@@ -1147,8 +1147,8 @@
       <c r="N13" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -1170,8 +1170,8 @@
       <c r="L14" s="14"/>
       <c r="M14" s="14"/>
       <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -1254,8 +1254,8 @@
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
-      <c r="O16" s="12"/>
-      <c r="P16" s="12"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -1301,10 +1301,10 @@
       <c r="N17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="O17" s="12" t="s">
+      <c r="O17" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="P17" s="12" t="s">
+      <c r="P17" s="16" t="s">
         <v>13</v>
       </c>
       <c r="Q17" s="1"/>
@@ -1344,8 +1344,8 @@
       <c r="N18" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
@@ -1385,8 +1385,8 @@
       <c r="N19" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
@@ -1419,8 +1419,8 @@
       <c r="M20" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
@@ -1567,8 +1567,8 @@
         <v>39</v>
       </c>
       <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
@@ -1596,8 +1596,8 @@
         <v>40</v>
       </c>
       <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
@@ -1625,8 +1625,8 @@
         <v>41</v>
       </c>
       <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
@@ -1745,8 +1745,8 @@
       <c r="L30" s="26"/>
       <c r="M30" s="26"/>
       <c r="N30" s="26"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="16"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
@@ -1778,8 +1778,8 @@
       <c r="N31" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="16"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
@@ -1801,8 +1801,8 @@
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
@@ -1921,8 +1921,8 @@
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="14"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="16"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
@@ -1954,8 +1954,8 @@
       <c r="N37" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
@@ -1977,8 +1977,8 @@
       <c r="L38" s="14"/>
       <c r="M38" s="14"/>
       <c r="N38" s="14"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="16"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
@@ -2107,8 +2107,8 @@
       <c r="N42" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="O42" s="14"/>
-      <c r="P42" s="14"/>
+      <c r="O42" s="16"/>
+      <c r="P42" s="16"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
@@ -2128,8 +2128,8 @@
       <c r="J43" s="14"/>
       <c r="L43" s="14"/>
       <c r="N43" s="14"/>
-      <c r="O43" s="14"/>
-      <c r="P43" s="14"/>
+      <c r="O43" s="16"/>
+      <c r="P43" s="16"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
@@ -2151,8 +2151,8 @@
       <c r="L44" s="14"/>
       <c r="M44" s="10"/>
       <c r="N44" s="10"/>
-      <c r="O44" s="10"/>
-      <c r="P44" s="10"/>
+      <c r="O44" s="16"/>
+      <c r="P44" s="16"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
@@ -2310,8 +2310,8 @@
       <c r="L49" s="14"/>
       <c r="M49" s="14"/>
       <c r="N49" s="14"/>
-      <c r="O49" s="14"/>
-      <c r="P49" s="14"/>
+      <c r="O49" s="16"/>
+      <c r="P49" s="16"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
@@ -2333,8 +2333,8 @@
       <c r="L50" s="14"/>
       <c r="M50" s="10"/>
       <c r="N50" s="10"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
+      <c r="O50" s="16"/>
+      <c r="P50" s="16"/>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
@@ -2496,8 +2496,8 @@
       <c r="L55" s="14"/>
       <c r="M55" s="14"/>
       <c r="N55" s="14"/>
-      <c r="O55" s="14"/>
-      <c r="P55" s="14"/>
+      <c r="O55" s="16"/>
+      <c r="P55" s="16"/>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
@@ -2519,8 +2519,8 @@
       <c r="L56" s="14"/>
       <c r="M56" s="10"/>
       <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="14"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="16"/>
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
@@ -2690,8 +2690,8 @@
       <c r="N61" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="O61" s="14"/>
-      <c r="P61" s="14"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
@@ -2723,8 +2723,8 @@
       <c r="N62" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="O62" s="3"/>
-      <c r="P62" s="3"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
@@ -2938,12 +2938,8 @@
       <c r="L69" s="28"/>
       <c r="M69" s="28"/>
       <c r="N69" s="28"/>
-      <c r="O69" s="5">
-        <v>45745</v>
-      </c>
-      <c r="P69" s="5">
-        <v>45746</v>
-      </c>
+      <c r="O69" s="28"/>
+      <c r="P69" s="28"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
@@ -2965,8 +2961,8 @@
       <c r="L70" s="28"/>
       <c r="M70" s="28"/>
       <c r="N70" s="28"/>
-      <c r="O70" s="16"/>
-      <c r="P70" s="16"/>
+      <c r="O70" s="28"/>
+      <c r="P70" s="28"/>
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
@@ -2990,8 +2986,8 @@
       <c r="L71" s="28"/>
       <c r="M71" s="28"/>
       <c r="N71" s="28"/>
-      <c r="O71" s="16"/>
-      <c r="P71" s="16"/>
+      <c r="O71" s="28"/>
+      <c r="P71" s="28"/>
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
@@ -3015,8 +3011,8 @@
       <c r="L72" s="28"/>
       <c r="M72" s="28"/>
       <c r="N72" s="28"/>
-      <c r="O72" s="16"/>
-      <c r="P72" s="16"/>
+      <c r="O72" s="28"/>
+      <c r="P72" s="28"/>
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
@@ -3038,8 +3034,8 @@
       <c r="L73" s="28"/>
       <c r="M73" s="28"/>
       <c r="N73" s="28"/>
-      <c r="O73" s="6"/>
-      <c r="P73" s="6"/>
+      <c r="O73" s="28"/>
+      <c r="P73" s="28"/>
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
@@ -3061,8 +3057,8 @@
       <c r="L74" s="28"/>
       <c r="M74" s="28"/>
       <c r="N74" s="28"/>
-      <c r="O74" s="16"/>
-      <c r="P74" s="16"/>
+      <c r="O74" s="28"/>
+      <c r="P74" s="28"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>

--- a/0_일정관리/일정.xlsx
+++ b/0_일정관리/일정.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{6E401FD5-689D-4F8A-AD59-0AA7F197EAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{B1E57D12-65B5-4E36-AB63-4A66C9F15ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21660" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21690" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="46">
   <si>
     <t>보여주기용</t>
   </si>
@@ -163,6 +163,10 @@
   </si>
   <si>
     <t>DAY18</t>
+  </si>
+  <si>
+    <t>UI 종료 예정</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -694,7 +698,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="33">
         <f ca="1">TODAY()</f>
-        <v>45701</v>
+        <v>45706</v>
       </c>
       <c r="K1" s="34"/>
       <c r="L1" s="35"/>
@@ -704,7 +708,7 @@
       <c r="N1" s="35"/>
       <c r="O1" s="3">
         <f ca="1">J69-J1</f>
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
@@ -2092,20 +2096,20 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="25"/>
-      <c r="J42" s="29" t="s">
+      <c r="J42" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="K42" s="29" t="s">
+      <c r="N42" s="29" t="s">
         <v>37</v>
-      </c>
-      <c r="L42" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="M42" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="N42" s="32" t="s">
-        <v>15</v>
       </c>
       <c r="O42" s="16"/>
       <c r="P42" s="16"/>
@@ -2126,7 +2130,9 @@
       <c r="H43" s="1"/>
       <c r="I43" s="25"/>
       <c r="J43" s="14"/>
-      <c r="L43" s="14"/>
+      <c r="L43" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="N43" s="14"/>
       <c r="O43" s="16"/>
       <c r="P43" s="16"/>
